--- a/тест-план.xlsx
+++ b/тест-план.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c781b0603d07078e/Рабочий стол/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c781b0603d07078e/Рабочий стол/Стратегия тестирования .xls Тест-план ^M чек-лист из файла/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_AD4DF75460589B3ACB72841E079C4A5A5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF5EB2F9-A851-4C5C-AFD4-ACA5CBD67EAD}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_AD4DF75460589B3ACB72841E079C4A5A5BDEDD8E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C852428-338B-4AC5-A6DF-E08EA797DB57}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="36">
   <si>
     <t>Цели доработки</t>
   </si>
@@ -318,7 +318,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -368,9 +368,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -382,9 +379,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -394,26 +388,35 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -775,13 +778,13 @@
     </row>
     <row r="6" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1"/>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -843,7 +846,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="121.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="22">
         <v>1</v>
       </c>
       <c r="B10" s="9"/>
@@ -856,230 +859,234 @@
       <c r="E10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="33">
         <v>0.4</v>
       </c>
       <c r="G10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="17" t="s">
+      <c r="J10" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="106.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
+      <c r="A11" s="23">
         <v>2</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="17"/>
+      <c r="C11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="19">
         <v>3</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="34">
         <v>0.4</v>
       </c>
-      <c r="G11" s="23" t="s">
+      <c r="G11" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="91.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
+      <c r="A12" s="25">
         <v>3</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="28">
         <v>8</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="35">
         <v>0.4</v>
       </c>
-      <c r="G12" s="23" t="s">
+      <c r="G12" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="I12" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="32" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="46.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
+      <c r="A13" s="23">
         <v>4</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="17"/>
+      <c r="C13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="19">
         <v>1</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="34">
         <v>0.4</v>
       </c>
-      <c r="G13" s="23" t="s">
+      <c r="G13" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="61.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28">
+      <c r="A14" s="25">
         <v>5</v>
       </c>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="28">
         <v>4</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="35">
         <v>0.4</v>
       </c>
-      <c r="G14" s="34" t="s">
+      <c r="G14" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="66" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25">
+      <c r="A15" s="23">
         <v>6</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="19">
         <v>5</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="34">
         <v>0.4</v>
       </c>
-      <c r="G15" s="23" t="s">
+      <c r="G15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="J15" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="66" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28">
+      <c r="A16" s="25">
         <v>7</v>
       </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
+      <c r="B16" s="26"/>
+      <c r="C16" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="28">
         <v>6</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="35">
         <v>0.4</v>
       </c>
-      <c r="G16" s="34" t="s">
+      <c r="G16" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="17" t="s">
+      <c r="J16" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="87" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+      <c r="A17" s="23">
         <v>8</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19" t="s">
+      <c r="B17" s="17"/>
+      <c r="C17" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="19">
         <v>7</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="34">
         <v>0.4</v>
       </c>
-      <c r="G17" s="23" t="s">
+      <c r="G17" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="J17" s="17" t="s">
+      <c r="J17" s="32" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="14" t="s">
         <v>9</v>
       </c>
